--- a/fiber_centers_periodic_relaxation_vf70_optimized.xlsx
+++ b/fiber_centers_periodic_relaxation_vf70_optimized.xlsx
@@ -41572,7 +41572,7 @@
         <v>0.35</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
